--- a/QTTB.xlsx
+++ b/QTTB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFED840E-5924-49B5-A5CA-C12B87796D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0842BAE1-B0F4-452D-BCBB-A83A8E9D5137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23865" yWindow="1440" windowWidth="22095" windowHeight="13845" xr2:uid="{7DD6825C-477A-469B-9BDA-D9596F8D7F36}"/>
+    <workbookView xWindow="4100" yWindow="4100" windowWidth="22360" windowHeight="16580" xr2:uid="{7DD6825C-477A-469B-9BDA-D9596F8D7F36}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>Price</t>
   </si>
@@ -57,9 +57,6 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Q324</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -102,10 +99,61 @@
     <t>Phase II AD</t>
   </si>
   <si>
-    <t>Phase II AA</t>
-  </si>
-  <si>
     <t>C3d mab</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Part B 36 week data, open label</t>
+  </si>
+  <si>
+    <t>Phase II "SIGNAL-AA" n=33 AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">week 24: </t>
+  </si>
+  <si>
+    <t>(31%) of ritlecitinib 200 mg + 50 mg group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(22%) of ritlectinib 200 mg + 30 mg group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(23%) of ritlectinib 50 mg group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(14%) of ritlectinib 30 mg group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2%) of 130 patients in the placebo group had a response based on SALT score 20 or less. </t>
+  </si>
+  <si>
+    <t>8 mg 29.6%; 12 mg 41.5% versus placebo 0.8% at 24 weeks</t>
+  </si>
+  <si>
+    <t>Part A 16% reduction vs. 2% for placebo</t>
+  </si>
+  <si>
+    <t>Phase III deuruxolitinib - proportion &lt;20</t>
+  </si>
+  <si>
+    <t>Phase III rit - proportion &lt; 20</t>
+  </si>
+  <si>
+    <t>week 36:</t>
+  </si>
+  <si>
+    <t>38.8% with 4-mg baricitinib</t>
+  </si>
+  <si>
+    <t>22.8% with 2-mg baricitinib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2% with placebo in BRAVE-AA1 </t>
+  </si>
+  <si>
+    <t>35.9%, 19.4%, and 3.3%, respectively, in BRAVE-AA2</t>
   </si>
 </sst>
 </file>
@@ -250,7 +298,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -258,9 +305,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -599,109 +647,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F39DD6-A552-4F68-9767-E26CBE854658}">
   <dimension ref="B2:L8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>45.24</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="5"/>
       <c r="J3" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2">
-        <v>12.076411999999999</v>
+        <v>16.956</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5"/>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>+K2*K3</f>
-        <v>546.33687887999997</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>339.12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="5"/>
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <v>89.078000000000003</v>
+        <v>50.750999999999998</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="6"/>
+      <c r="H6" s="5"/>
       <c r="J6" t="s">
         <v>4</v>
       </c>
@@ -709,33 +741,28 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="6"/>
+      <c r="H7" s="5"/>
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="2">
         <f>+K4-K5+K6</f>
-        <v>457.25887888</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
+        <v>288.36900000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -747,60 +774,143 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ECC032-FC17-4C3F-959C-6CA4DA50E65D}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C7" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C7" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C10" s="15" t="s">
-        <v>21</v>
+    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C14" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C23" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D29" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D31" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{F0ACC97B-4E1D-42BA-95CC-7683B88BE57B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>